--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_PSC.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -629,44 +629,44 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
         <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>PSC_G._ROSADO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>G. Rosado</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -740,7 +928,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: G. Rosado (12 L)</t>
+          <t>Maior volume: M. Landdeck (26 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +940,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: M. Landdeck (8 3PA)</t>
+          <t>Maior volume 3pt: M. Landdeck (16 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +952,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: G. Rosado (1.3 pts/shot)</t>
+          <t>Mais eficaz: G. Rosado (1.5 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +964,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Paint Non-RA (25 L)</t>
+          <t>Zona mais usada: Above the Break 3 (38 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +976,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (70.0%)</t>
+          <t>Zona mais eficaz: Restricted Area (57.1%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -928,180 +1116,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>16</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>6</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>12</v>
       </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>7</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1297,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1126,34 +1314,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1168,59 +1356,59 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>55.6%</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1230,7 +1418,7 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1245,66 +1433,66 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1313,75 +1501,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1390,75 +1578,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
         <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1476,34 +1664,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1511,28 +1699,115 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSC_P._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>6</v>
       </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S9"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1543,7 +1818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1676,143 +1951,143 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>12</v>
       </c>
-      <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
         <v>6</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1821,60 +2096,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1882,21 +2157,329 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PSC_J._GREWAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Grewal</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1907,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2010,29 +2593,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2040,55 +2623,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2096,227 +2679,227 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_H._SOTTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>H. Sotta</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2324,29 +2907,29 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="n">
         <v>6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2358,51 +2941,51 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_H._SOTTA</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2414,40 +2997,96 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
         <v>6</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSC_T._COLEMAN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2458,28 +3097,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2554,106 +3376,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C3" t="n">
         <v>20</v>
       </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2663,32 +3485,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2698,7 +3520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2716,11 +3538,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
@@ -2733,21 +3555,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2773,7 +3595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2879,47 +3701,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2927,104 +3749,104 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3033,45 +3855,45 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -3079,7 +3901,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -3103,57 +3925,57 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="6">
@@ -3169,37 +3991,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3207,15 +4029,15 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3223,18 +4045,18 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3243,127 +4065,127 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -3383,41 +4205,131 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSC_P._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
+      <c r="P10" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P9"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3428,7 +4340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3514,74 +4426,74 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -3594,35 +4506,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3639,12 +4551,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3653,43 +4565,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3698,36 +4610,216 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PSC_P._BASTOS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSC_J._GREWAL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Grewal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_PSC.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,83 +590,83 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="E2" t="n">
+        <v>188</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>44.1%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>115</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>38.6%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>79</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="I2" t="n">
+        <v>73</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30.1%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>38.8%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>58</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>51.7%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
         <v>53</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>24.5%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>40.2%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>38</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>31.6%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>35</v>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
         <v>6</v>
       </c>
-      <c r="T2" t="n">
-        <v>11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>11</v>
-      </c>
       <c r="V2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W2" t="n">
         <v>7</v>
-      </c>
-      <c r="W2" t="n">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2" t="n">
         <v>12</v>
       </c>
-      <c r="E2" t="n">
-        <v>11</v>
-      </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -802,12 +802,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,81 +816,216 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
         <v>9</v>
       </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PSC_J._GREWAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Grewal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>48.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -928,7 +1063,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: M. Landdeck (26 L)</t>
+          <t>Maior volume: M. Landdeck (43 L)</t>
         </is>
       </c>
     </row>
@@ -940,7 +1075,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: M. Landdeck (16 3PA)</t>
+          <t>Maior volume 3pt: M. Landdeck (26 3PA)</t>
         </is>
       </c>
     </row>
@@ -964,7 +1099,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (38 L)</t>
+          <t>Zona mais usada: Paint Non-RA (58 L)</t>
         </is>
       </c>
     </row>
@@ -976,7 +1111,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (57.1%)</t>
+          <t>Zona mais eficaz: Restricted Area (60.0%)</t>
         </is>
       </c>
     </row>
@@ -1125,34 +1260,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>26</v>
       </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>16</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1160,16 +1295,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -1177,14 +1312,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1202,17 +1337,17 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3" t="n">
         <v>22</v>
       </c>
-      <c r="D3" t="n">
-        <v>16</v>
-      </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1225,7 +1360,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1237,11 +1372,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1250,11 +1385,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1270,55 +1405,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1327,157 +1462,157 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
         <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1485,140 +1620,140 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1626,12 +1761,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1639,91 +1774,91 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_H._SOTTA</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1732,78 +1867,78 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PSC_P._OLIVEIRA</t>
+          <t>PSC_H._SOTTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>H. Sotta</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1818,7 +1953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1955,17 +2090,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2" t="n">
         <v>22</v>
       </c>
-      <c r="F2" t="n">
-        <v>16</v>
-      </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -1977,7 +2112,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1986,11 +2121,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1999,11 +2134,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2013,66 +2148,66 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -2087,21 +2222,21 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2109,106 +2244,106 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>15</v>
       </c>
-      <c r="H4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2217,178 +2352,178 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>21</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>6</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>3</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
         <v>6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2398,88 +2533,165 @@
         <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" t="n">
         <v>5</v>
       </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2593,29 +2805,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2623,18 +2835,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2649,23 +2861,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
         <v>15</v>
@@ -2679,11 +2891,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2705,26 +2917,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="n">
         <v>17</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13</v>
       </c>
       <c r="I4" t="n">
         <v>0.8</v>
@@ -2735,127 +2947,127 @@
         </is>
       </c>
       <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
         <v>5</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_H._SOTTA</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
         <v>4</v>
@@ -2864,68 +3076,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_H._SOTTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>H. Sotta</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>4</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4</v>
-      </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_P._OLIVEIRA</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2941,33 +3153,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>6</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
         <v>7</v>
@@ -2997,14 +3209,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I9" t="n">
         <v>1.5</v>
@@ -3015,18 +3227,18 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3053,29 +3265,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>29</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>15</v>
       </c>
-      <c r="H10" t="n">
-        <v>19</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>9</v>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -3097,7 +3309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3200,23 +3412,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
         <v>15</v>
@@ -3230,11 +3442,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -3247,61 +3459,117 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>61.5%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>26</v>
-      </c>
-      <c r="H3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>5</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26.9%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3376,56 +3644,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3433,49 +3701,49 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3485,25 +3753,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3520,25 +3788,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3555,7 +3823,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -3565,15 +3833,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3715,16 +3983,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3732,40 +4000,40 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>26</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>16</v>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3">
@@ -3785,11 +4053,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3798,11 +4066,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3819,11 +4087,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -3841,25 +4109,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3868,11 +4136,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3889,122 +4157,122 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4012,12 +4280,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4025,113 +4293,113 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4139,12 +4407,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4152,51 +4420,51 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_H._SOTTA</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4205,68 +4473,68 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>7</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>42.9%</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PSC_P._OLIVEIRA</t>
+          <t>PSC_H._SOTTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>H. Sotta</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4275,11 +4543,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4288,16 +4556,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -4305,27 +4573,27 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -4340,7 +4608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4416,129 +4684,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PSC_G._ROSADO</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>G. Rosado</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_G._ROSADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>G. Rosado</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4565,29 +4833,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -4596,21 +4864,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -4620,15 +4888,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4641,39 +4909,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4686,43 +4954,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -4731,43 +4999,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -4776,50 +5044,230 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>29.4%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="H13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>11.6%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PSC_P._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_PSC.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>188</v>
+        <v>239</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="E2" t="n">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -629,28 +629,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>68</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>32.4%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>58</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>51.7%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -663,10 +663,10 @@
         <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -771,29 +771,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -816,25 +816,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -857,11 +857,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
@@ -871,161 +871,251 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PSC_J._GREWAL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Grewal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>34.5%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PSC_L._RAHAMA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>48.1%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K7"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1063,7 +1153,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: M. Landdeck (43 L)</t>
+          <t>Maior volume: M. Landdeck (55 L)</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1165,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: M. Landdeck (26 3PA)</t>
+          <t>Maior volume 3pt: M. Landdeck (35 3PA)</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1189,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Paint Non-RA (58 L)</t>
+          <t>Zona mais usada: Above the Break 3 (68 L)</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1201,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (60.0%)</t>
+          <t>Zona mais eficaz: Restricted Area (64.4%)</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1233,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
@@ -1260,30 +1350,30 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" t="n">
         <v>43</v>
       </c>
-      <c r="D2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30.9%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>35</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>32.6%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>26</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1295,11 +1385,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1308,18 +1398,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1337,30 +1427,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1368,28 +1458,28 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>13</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1414,17 +1504,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1437,11 +1527,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1449,11 +1539,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1462,18 +1552,18 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1491,30 +1581,30 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1526,31 +1616,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1568,30 +1658,30 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
         <v>20</v>
       </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>14</v>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1603,31 +1693,31 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1645,22 +1735,22 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
         <v>16</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -1672,7 +1762,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1680,11 +1770,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1693,18 +1783,18 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1713,43 +1803,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1761,12 +1851,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1774,59 +1864,59 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_P._OLIVEIRA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1834,16 +1924,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1851,17 +1941,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1876,7 +1966,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -1886,36 +1976,36 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>20.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>25.0%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1935,10 +2025,10 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
         <v>5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1953,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1969,7 +2059,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -2090,55 +2180,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2148,7 +2238,7 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2163,33 +2253,33 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2198,16 +2288,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -2222,7 +2312,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -2231,12 +2321,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2244,153 +2334,153 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="E5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>17</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>13</v>
       </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>84.6%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2398,29 +2488,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2429,31 +2519,31 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -2462,12 +2552,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2475,34 +2565,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -2510,7 +2600,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2519,179 +2609,256 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>29</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>31.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>6</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>4</v>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSC_H._SOTTA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H. Sotta</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
         <v>7</v>
       </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S9"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2805,26 +2972,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H2" t="n">
         <v>43</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35</v>
       </c>
       <c r="I2" t="n">
         <v>0.8</v>
@@ -2835,55 +3002,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2891,74 +3058,74 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>84.6%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>22</v>
-      </c>
-      <c r="H4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2973,29 +3140,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3003,11 +3170,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -3029,26 +3196,26 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="n">
         <v>20</v>
-      </c>
-      <c r="H6" t="n">
-        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>0.7</v>
@@ -3059,18 +3226,18 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3085,29 +3252,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3115,18 +3282,18 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -3141,7 +3308,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3157,13 +3324,13 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
         <v>16</v>
       </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -3171,18 +3338,18 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3197,48 +3364,48 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H9" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I9" t="n">
         <v>1.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3265,17 +3432,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3283,11 +3450,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -3450,7 +3617,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -3468,26 +3635,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I3" t="n">
         <v>0.8</v>
@@ -3498,18 +3665,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3524,26 +3691,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>55</v>
+      </c>
+      <c r="H4" t="n">
         <v>43</v>
-      </c>
-      <c r="H4" t="n">
-        <v>35</v>
       </c>
       <c r="I4" t="n">
         <v>0.8</v>
@@ -3554,18 +3721,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3644,21 +3811,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3666,49 +3833,49 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3718,25 +3885,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -3753,25 +3920,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3788,7 +3955,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -3798,7 +3965,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3806,7 +3973,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3823,25 +3990,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3871,7 +4038,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -3983,11 +4150,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3996,11 +4163,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4009,27 +4176,27 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4049,28 +4216,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4079,27 +4246,27 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -4123,11 +4290,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4136,11 +4303,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4149,19 +4316,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -4173,7 +4340,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="5">
@@ -4193,29 +4360,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4223,23 +4390,23 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -4263,53 +4430,53 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>27</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>20</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -4333,11 +4500,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4346,36 +4513,36 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -4383,18 +4550,18 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_P._OLIVEIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>P. Oliveira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4407,12 +4574,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4420,51 +4587,51 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_P._OLIVEIRA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4473,16 +4640,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4490,12 +4657,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -4507,23 +4674,23 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
@@ -4543,11 +4710,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4565,35 +4732,35 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -4608,7 +4775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4698,25 +4865,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -4743,7 +4910,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
         <v>8</v>
@@ -4753,15 +4920,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4784,36 +4951,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -4829,78 +4996,78 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSC_L._RAHAMA</t>
+          <t>PSC_T._COLEMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>37.1%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>55.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -4909,57 +5076,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSC_J._GREWAL</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Grewal</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSC_P._BASTOS</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4968,43 +5135,43 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSC_T._COLEMAN</t>
+          <t>PSC_D._FRAGOSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5013,7 +5180,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -5023,42 +5190,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_J._GREWAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -5068,67 +5235,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PSC_D._FRAGOSO</t>
+          <t>PSC_M._LANDDECK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>M. Landdeck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
         <v>6</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5148,25 +5315,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -5179,43 +5346,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PSC_M._LANDDECK</t>
+          <t>PSC_L._RAHAMA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M. Landdeck</t>
+          <t>L. Rahama</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -5224,12 +5391,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PSC_P._OLIVEIRA</t>
+          <t>PSC_P._BASTOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5238,25 +5405,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -5266,8 +5433,233 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10.9%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PSC_P._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PSC_D._FRAGOSO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PSC_H._SOTTA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H. Sotta</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PSC_M._LANDDECK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>